--- a/RBI01S.xlsx
+++ b/RBI01S.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="108">
   <si>
     <t/>
   </si>
@@ -115,151 +115,145 @@
     <t>11</t>
   </si>
   <si>
-    <t>10038053</t>
-  </si>
-  <si>
-    <t>PEAR YALIE BZR WHL</t>
+    <t>10019138</t>
+  </si>
+  <si>
+    <t>PEAR CENTURY BAZ WHL</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>10038054</t>
+  </si>
+  <si>
+    <t>PEAR XIANG LI BZ WHL</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>10008574</t>
+  </si>
+  <si>
+    <t>ANGGUR AUTUM WHL</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>10015367</t>
+  </si>
+  <si>
+    <t>APL FUJI BLS BAZ WHL</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>10013184</t>
+  </si>
+  <si>
+    <t>JERUK MURCOTT  WHL</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>20130893</t>
+  </si>
+  <si>
+    <t>JERUK CARA-CARA WHL</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20130892</t>
+  </si>
+  <si>
+    <t>AGR SHINE MSCT BAZAR</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>20131582</t>
+  </si>
+  <si>
+    <t>JRK SANTANG PCK</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>20111859</t>
+  </si>
+  <si>
+    <t>OLAH JRK SUNKIST WHL</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>20117327</t>
+  </si>
+  <si>
+    <t>BUAH POT JRK NAVEL</t>
+  </si>
+  <si>
+    <t>PT,(E-1J)</t>
+  </si>
+  <si>
+    <t>20117340</t>
+  </si>
+  <si>
+    <t>POT PEAR SW BAZ PCK</t>
+  </si>
+  <si>
+    <t>20117345</t>
+  </si>
+  <si>
+    <t>POT APEL FJ BAZ PCK</t>
+  </si>
+  <si>
+    <t>20137134</t>
+  </si>
+  <si>
+    <t>JERUK IMPORT PCK</t>
+  </si>
+  <si>
+    <t>20111884</t>
+  </si>
+  <si>
+    <t>POT PEAR SW BAZ WHL</t>
+  </si>
+  <si>
+    <t>20138452</t>
+  </si>
+  <si>
+    <t>OLAH PEAR CENT WHL</t>
+  </si>
+  <si>
+    <t>20111812</t>
+  </si>
+  <si>
+    <t>BUAH PT PEAR CEN PCS</t>
+  </si>
+  <si>
+    <t>20093014</t>
+  </si>
+  <si>
+    <t>POT CAMPUR IMP PCK</t>
+  </si>
+  <si>
+    <t>20139147</t>
+  </si>
+  <si>
+    <t>B/O JERUK SUNKIST CR</t>
   </si>
   <si>
     <t>12</t>
-  </si>
-  <si>
-    <t>10019138</t>
-  </si>
-  <si>
-    <t>PEAR CENTURY BAZ WHL</t>
-  </si>
-  <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>10038054</t>
-  </si>
-  <si>
-    <t>PEAR XIANG LI BZ WHL</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>10008574</t>
-  </si>
-  <si>
-    <t>ANGGUR AUTUM WHL</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>10015367</t>
-  </si>
-  <si>
-    <t>APL FUJI BLS BAZ WHL</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>10013184</t>
-  </si>
-  <si>
-    <t>JERUK MURCOTT  WHL</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>20130893</t>
-  </si>
-  <si>
-    <t>JERUK CARA-CARA WHL</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>20130892</t>
-  </si>
-  <si>
-    <t>AGR SHINE MSCT BAZAR</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>20131582</t>
-  </si>
-  <si>
-    <t>JRK SANTANG PCK</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>20111859</t>
-  </si>
-  <si>
-    <t>OLAH JRK SUNKIST WHL</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>20117327</t>
-  </si>
-  <si>
-    <t>BUAH POT JRK NAVEL</t>
-  </si>
-  <si>
-    <t>PT,(E-1J)</t>
-  </si>
-  <si>
-    <t>20117340</t>
-  </si>
-  <si>
-    <t>POT PEAR SW BAZ PCK</t>
-  </si>
-  <si>
-    <t>20117345</t>
-  </si>
-  <si>
-    <t>POT APEL FJ BAZ PCK</t>
-  </si>
-  <si>
-    <t>20137134</t>
-  </si>
-  <si>
-    <t>JERUK IMPORT PCK</t>
-  </si>
-  <si>
-    <t>20111884</t>
-  </si>
-  <si>
-    <t>POT PEAR SW BAZ WHL</t>
-  </si>
-  <si>
-    <t>20138452</t>
-  </si>
-  <si>
-    <t>OLAH PEAR CENT WHL</t>
-  </si>
-  <si>
-    <t>20111812</t>
-  </si>
-  <si>
-    <t>BUAH PT PEAR CEN PCS</t>
-  </si>
-  <si>
-    <t>20093014</t>
-  </si>
-  <si>
-    <t>POT CAMPUR IMP PCK</t>
-  </si>
-  <si>
-    <t>20139147</t>
-  </si>
-  <si>
-    <t>B/O JERUK SUNKIST CR</t>
   </si>
   <si>
     <t>,(E-1J)</t>
@@ -733,7 +727,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -1141,7 +1135,7 @@
         <v>60</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -1155,13 +1149,13 @@
         <v>3</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>63</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1178,19 +1172,19 @@
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>68</v>
-      </c>
       <c r="C23" s="1" t="s">
         <v>3</v>
       </c>
@@ -1198,19 +1192,19 @@
         <v>8</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>70</v>
-      </c>
       <c r="C24" s="1" t="s">
         <v>3</v>
       </c>
@@ -1218,19 +1212,19 @@
         <v>8</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B25" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="C25" s="1" t="s">
         <v>3</v>
       </c>
@@ -1238,19 +1232,19 @@
         <v>8</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>5</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B26" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="C26" s="1" t="s">
         <v>3</v>
       </c>
@@ -1258,7 +1252,7 @@
         <v>8</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="F26" s="1" t="s">
         <v>30</v>
@@ -1266,11 +1260,11 @@
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>76</v>
-      </c>
       <c r="C27" s="1" t="s">
         <v>3</v>
       </c>
@@ -1278,19 +1272,19 @@
         <v>8</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>30</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
@@ -1298,38 +1292,38 @@
         <v>8</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>66</v>
+        <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>33</v>
-      </c>
       <c r="F29" s="1" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
@@ -1341,7 +1335,7 @@
         <v>36</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>83</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -1358,10 +1352,10 @@
         <v>8</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>66</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -1378,7 +1372,7 @@
         <v>8</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="F32" s="1" t="s">
         <v>5</v>
@@ -1398,7 +1392,7 @@
         <v>8</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>54</v>
+        <v>90</v>
       </c>
       <c r="F33" s="1" t="s">
         <v>5</v>
@@ -1406,10 +1400,10 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>3</v>
@@ -1418,7 +1412,7 @@
         <v>8</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F34" s="1" t="s">
         <v>5</v>
@@ -1426,10 +1420,10 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>3</v>
@@ -1438,7 +1432,7 @@
         <v>8</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>5</v>
@@ -1446,10 +1440,10 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>3</v>
@@ -1458,7 +1452,7 @@
         <v>8</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>5</v>
@@ -1466,10 +1460,10 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>3</v>
@@ -1478,63 +1472,43 @@
         <v>8</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F37" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="F38" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D39" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="C39" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>107</v>
-      </c>
       <c r="E39" s="1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B40" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C40" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="E40" s="1" t="s">
         <v>8</v>
       </c>
     </row>

--- a/RBI01S.xlsx
+++ b/RBI01S.xlsx
@@ -268,7 +268,7 @@
     <t>20129832</t>
   </si>
   <si>
-    <t>APEL CHERRY/STRAWBRY</t>
+    <t>APEL CHERRY</t>
   </si>
   <si>
     <t>20117282</t>
